--- a/2_Risk_Management/MT-ISMS-RR-001_v1.1_risk-register.xlsx
+++ b/2_Risk_Management/MT-ISMS-RR-001_v1.1_risk-register.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="145">
   <si>
     <t>MunichTech GmbH</t>
   </si>
@@ -49,7 +49,7 @@
     <t>Effective Date</t>
   </si>
   <si>
-    <t>[Date]</t>
+    <t/>
   </si>
   <si>
     <t>Austin Bond, Junior GRC Consultant</t>
@@ -170,7 +170,7 @@
     <t>CEO</t>
   </si>
   <si>
-    <t>[Senior GRC Partner Name], CISM, ISO 27000 LA</t>
+    <t>Dr. Andreas Kellermann, CISM, ISO 27001 LA</t>
   </si>
   <si>
     <t>Risk ID</t>
@@ -588,7 +588,7 @@
     <t>Implement Just-In-Time (JIT) access via AWS IAM Identity Center. Okta SCIM provisioning linked to BambooHR for automated access revocation upon termination. Regular access reviews (quarterly) managed via Jira workflows.</t>
   </si>
   <si>
-    <t>Deploy CrowdStrike Falcon EDR to all endpoints via Microsoft Intune. Note: Implementation requires prior Betriebsvereinbarung per BetrVG § 87 due to behavior monitoring capabilities. Enforce FIDO2/WebAuthn hardware keys.</t>
+    <t>Deploy CrowdStrike Falcon EDR to all endpoints via Microsoft Intune. Deployment is covered by the signed Betriebsvereinbarung MT-WorksCouncil-CrowdStrike-v1.2 (BetrVG § 87); endpoint telemetry is confined to security purposes and is not used for performance or behaviour monitoring. Enforce FIDO2/WebAuthn hardware keys.</t>
   </si>
   <si>
     <t>Accepted by Ops Manager. Building managed by third-party landlord. Enforce MT-POL-007 (Clear Desk Policy) and MDM auto-lock screens (5 mins). Corporate network uses 802.1X NAC to prevent unauthorized hardware from routing.</t>
@@ -603,7 +603,7 @@
     <t>Utilize AWS KMS with automated key rotation (annual). Enforce strict separation of duties: Developers cannot access production KMS key material. RDS snapshots replicated to an isolated, immutable vault account.</t>
   </si>
   <si>
-    <t>Accepted by CEO. Budget for dedicated CISO deferred to Q1 2027. Mitigation: Retain external Big 4 GRC advisory for fractional support and maintain exhaustive runbooks in Confluence to ensure continuity.</t>
+    <t>Accepted by CEO on 20 April 2026. Budget for a dedicated full-time CISO approved at the FY2026 Management Review; recruitment to conclude in Q1 2027 (target 31 March 2027). Mitigation: Retain external Big 4 GRC advisory for fractional support and maintain exhaustive runbooks in Confluence to ensure continuity.</t>
   </si>
   <si>
     <t>Deploy Atlassian Data Loss Prevention (DLP) to scan for Regex patterns matching AWS keys and credit card numbers. Implement GitHub Secret Scanning to prevent commits containing secrets. Update Developer Onboarding training.</t>
@@ -1318,6 +1318,12 @@
   </si>
   <si>
     <t>Version 1.1 — BaFin BAIT references replaced with DORA (Reg. (EU) 2022/2554), applicable from 17 January 2025. No risk score, rating or treatment decision changed.</t>
+  </si>
+  <si>
+    <t>20 April 2026</t>
+  </si>
+  <si>
+    <t>Executive Risk Acceptance — RR-013 (Key Person Dependency). Accepted by Dr. Katharina Vogt, CEO / Managing Director, on 20 April 2026 at the FY2026 Management Review, on the terms recorded above: a dedicated full-time CISO is to be recruited with external Big 4 GRC advisory retained as interim cover. Signature retained in DocuSign envelope MT-RR-013-ACCEPT-2026-04. This note is the executive acceptance that closes internal audit finding AUD-02 and is the evidence cited in MT-ISMS-CAP-001.</t>
   </si>
 </sst>
 </file>
@@ -1948,7 +1954,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:P32"/>
+  <dimension ref="B3:P33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -2002,7 +2008,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="H8" s="4"/>
       <c r="K8" s="1"/>
@@ -2837,6 +2843,11 @@
     <row r="32">
       <c r="B32" s="20" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="20" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
